--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-bristol-stool-chart</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-bristol-stool-chart</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="499">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3689,7 +3681,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3707,23 +3699,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3750,10 +3742,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3761,13 +3753,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -3811,7 +3803,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -3829,10 +3821,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -3874,10 +3866,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -3885,14 +3877,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3914,16 +3906,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -3933,29 +3925,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -3972,7 +3964,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -3987,30 +3979,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4033,19 +4025,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4094,7 +4086,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4109,19 +4101,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4129,10 +4121,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4155,16 +4147,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4214,7 +4206,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4235,13 +4227,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4249,14 +4241,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4275,19 +4267,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4336,7 +4328,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4351,19 +4343,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4371,14 +4363,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4397,19 +4389,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4458,7 +4450,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4473,19 +4465,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4493,10 +4485,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4519,16 +4511,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4578,7 +4570,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4599,13 +4591,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4613,10 +4605,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4639,17 +4631,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4698,7 +4690,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4713,19 +4705,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4733,10 +4725,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4759,19 +4751,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4820,7 +4812,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4829,7 +4821,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -4838,27 +4830,27 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4881,13 +4873,13 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4938,7 +4930,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4962,7 +4954,7 @@
         <v>18</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
@@ -4973,10 +4965,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5005,7 +4997,7 @@
         <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>139</v>
@@ -5046,19 +5038,19 @@
         <v>18</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AC26" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AC26" t="s" s="2">
+      <c r="AD26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5082,7 +5074,7 @@
         <v>18</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>18</v>
@@ -5093,10 +5085,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5119,19 +5111,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5180,7 +5172,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5192,19 +5184,19 @@
         <v>18</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AK27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5215,10 +5207,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5244,20 +5236,20 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q28" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="P28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q28" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="R28" t="s" s="2">
         <v>18</v>
@@ -5281,28 +5273,28 @@
         <v>179</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5323,10 +5315,10 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>18</v>
@@ -5337,10 +5329,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5363,17 +5355,17 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5383,46 +5375,46 @@
         <v>18</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5443,10 +5435,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5457,10 +5449,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5486,14 +5478,14 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -5503,46 +5495,46 @@
         <v>18</v>
       </c>
       <c r="S30" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5551,7 +5543,7 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5563,10 +5555,10 @@
         <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>18</v>
@@ -5577,10 +5569,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5606,16 +5598,16 @@
         <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5664,7 +5656,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5685,10 +5677,10 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>18</v>
@@ -5699,10 +5691,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5728,16 +5720,16 @@
         <v>188</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5762,14 +5754,14 @@
         <v>18</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>18</v>
       </c>
@@ -5786,7 +5778,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5795,7 +5787,7 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>102</v>
@@ -5810,7 +5802,7 @@
         <v>133</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -5821,14 +5813,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5850,16 +5842,16 @@
         <v>188</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -5884,14 +5876,14 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
       </c>
@@ -5908,7 +5900,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5926,27 +5918,27 @@
         <v>18</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5969,19 +5961,19 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -6030,7 +6022,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6051,10 +6043,10 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -6065,10 +6057,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6094,13 +6086,13 @@
         <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6126,14 +6118,14 @@
         <v>18</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>18</v>
       </c>
@@ -6150,7 +6142,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6168,27 +6160,27 @@
         <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6214,16 +6206,16 @@
         <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
@@ -6248,14 +6240,14 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
       </c>
@@ -6272,7 +6264,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6293,10 +6285,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6307,10 +6299,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6333,16 +6325,16 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6392,7 +6384,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6410,27 +6402,27 @@
         <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6453,16 +6445,16 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6512,7 +6504,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6530,27 +6522,27 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6573,19 +6565,19 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6634,7 +6626,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6646,19 +6638,19 @@
         <v>18</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AK39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6669,10 +6661,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6695,13 +6687,13 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6752,7 +6744,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6776,7 +6768,7 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -6787,10 +6779,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6819,7 +6811,7 @@
         <v>137</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>139</v>
@@ -6872,7 +6864,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6896,7 +6888,7 @@
         <v>18</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -6907,14 +6899,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6936,10 +6928,10 @@
         <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>139</v>
@@ -6994,7 +6986,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7029,10 +7021,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7055,13 +7047,13 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7112,7 +7104,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7121,7 +7113,7 @@
         <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>102</v>
@@ -7133,10 +7125,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7147,10 +7139,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7173,13 +7165,13 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7230,7 +7222,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7239,7 +7231,7 @@
         <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>102</v>
@@ -7251,10 +7243,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7265,10 +7257,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7294,16 +7286,16 @@
         <v>188</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>18</v>
@@ -7331,11 +7323,11 @@
         <v>114</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>18</v>
       </c>
@@ -7352,7 +7344,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7370,13 +7362,13 @@
         <v>18</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="AN45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7387,10 +7379,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7416,16 +7408,16 @@
         <v>188</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
@@ -7450,14 +7442,14 @@
         <v>18</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7474,7 +7466,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7492,13 +7484,13 @@
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="AN46" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7509,10 +7501,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7535,17 +7527,17 @@
         <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7594,7 +7586,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7618,7 +7610,7 @@
         <v>18</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>18</v>
@@ -7629,10 +7621,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7655,13 +7647,13 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7712,7 +7704,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7733,10 +7725,10 @@
         <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>18</v>
@@ -7747,10 +7739,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7773,16 +7765,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7832,7 +7824,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7853,10 +7845,10 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>18</v>
@@ -7867,10 +7859,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7893,16 +7885,16 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7952,7 +7944,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7973,10 +7965,10 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -7987,10 +7979,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8013,19 +8005,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8074,7 +8066,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8095,10 +8087,10 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>18</v>
@@ -8109,10 +8101,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8135,13 +8127,13 @@
         <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8192,7 +8184,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8216,7 +8208,7 @@
         <v>18</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
@@ -8227,10 +8219,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8259,7 +8251,7 @@
         <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -8312,7 +8304,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8336,7 +8328,7 @@
         <v>18</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8347,14 +8339,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8376,10 +8368,10 @@
         <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -8434,7 +8426,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8469,10 +8461,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8498,16 +8490,16 @@
         <v>188</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N55" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O55" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>18</v>
@@ -8532,14 +8524,14 @@
         <v>18</v>
       </c>
       <c r="X55" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y55" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y55" t="s" s="2">
+      <c r="Z55" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
       </c>
@@ -8556,7 +8548,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8574,16 +8566,16 @@
         <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>18</v>
@@ -8591,10 +8583,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8617,19 +8609,19 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O56" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8678,7 +8670,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8696,27 +8688,27 @@
         <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8742,16 +8734,16 @@
         <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8776,14 +8768,14 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
       </c>
@@ -8800,7 +8792,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8809,7 +8801,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -8824,7 +8816,7 @@
         <v>133</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>18</v>
@@ -8835,14 +8827,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8864,16 +8856,16 @@
         <v>188</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -8898,14 +8890,14 @@
         <v>18</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>18</v>
       </c>
@@ -8922,7 +8914,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8940,27 +8932,27 @@
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8986,16 +8978,16 @@
         <v>80</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N59" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9044,7 +9036,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9065,10 +9057,10 @@
         <v>18</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-bristol-stool-chart.xlsx
+++ b/StructureDefinition-onc-bristol-stool-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
